--- a/spec-tech/ig/StructureDefinition-pdlgcAuthor.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcAuthor.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
